--- a/ORDIA_公開前チェックリスト_rev3.xlsx
+++ b/ORDIA_公開前チェックリスト_rev3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sahib\Desktop\Claude\Onevio Lp\Onevio_ORDIA_LP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FCDA0A5-3BBC-44E6-88CD-3C55DB4A333A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF705841-6330-4DFD-AD23-F0ADEDBAAD86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{095DE823-2A0A-43B1-8709-F9DC5D05F209}"/>
   </bookViews>
@@ -195,9 +195,6 @@
     <t>【修正済】公開日に合わせて2026年7月8日に確定し、利用規約・プライバシーポリシー両方の「施行日」「制定」を更新済み。</t>
   </si>
   <si>
-    <t>会社情報（代表取締役 相楽 賢哉・住所・電話・info@sagbrain.com）が正しいか確認してください。</t>
-  </si>
-  <si>
     <t>公式サイト（sagbrain.com/company）と照合し一致を確認済み。最終的に登記・名刺で再確認。</t>
   </si>
   <si>
@@ -382,6 +379,10 @@
   </si>
   <si>
     <t>公開したあと（水曜）に、表示と動作を最終確認。</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>会社情報（代表取締役 相楽 賢哉・住所・電話・info@sagbrain.com）が正しいか確認。</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -942,7 +943,7 @@
         <v>16</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>12</v>
@@ -982,7 +983,7 @@
         <v>20</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>12</v>
@@ -1319,13 +1320,13 @@
         <v>2</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D25" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D25" s="3" t="s">
-        <v>56</v>
-      </c>
       <c r="E25" s="4" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1339,13 +1340,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D26" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>58</v>
-      </c>
       <c r="E26" s="4" t="s">
-        <v>12</v>
+        <v>70</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
@@ -1359,10 +1360,10 @@
         <v>4</v>
       </c>
       <c r="C27" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>60</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>12</v>
@@ -1373,17 +1374,17 @@
     </row>
     <row r="28" spans="1:8" ht="33">
       <c r="A28" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B28" s="3">
         <v>1</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
@@ -1391,17 +1392,17 @@
     </row>
     <row r="29" spans="1:8" ht="33">
       <c r="A29" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B29" s="3">
         <v>2</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1409,13 +1410,13 @@
     </row>
     <row r="30" spans="1:8" ht="49.5">
       <c r="A30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B30" s="3">
         <v>3</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="4" t="s">
@@ -1427,17 +1428,17 @@
     </row>
     <row r="31" spans="1:8" ht="49.5">
       <c r="A31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B31" s="3">
         <v>4</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1445,13 +1446,13 @@
     </row>
     <row r="32" spans="1:8" ht="33">
       <c r="A32" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B32" s="3">
         <v>5</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="4" t="s">
@@ -1463,17 +1464,17 @@
     </row>
     <row r="33" spans="1:8" ht="33">
       <c r="A33" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B33" s="3">
         <v>6</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
@@ -1481,17 +1482,17 @@
     </row>
     <row r="34" spans="1:8" ht="33">
       <c r="A34" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B34" s="3">
         <v>7</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -1499,17 +1500,17 @@
     </row>
     <row r="35" spans="1:8" ht="33">
       <c r="A35" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B35" s="3">
         <v>8</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -1517,13 +1518,13 @@
     </row>
     <row r="36" spans="1:8" ht="33">
       <c r="A36" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B36" s="3">
         <v>9</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="4" t="s">
@@ -1535,13 +1536,13 @@
     </row>
     <row r="37" spans="1:8" ht="33">
       <c r="A37" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B37" s="3">
         <v>10</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="4" t="s">
@@ -1553,17 +1554,17 @@
     </row>
     <row r="38" spans="1:8" ht="33">
       <c r="A38" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B38" s="3">
         <v>11</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1571,13 +1572,13 @@
     </row>
     <row r="39" spans="1:8" ht="33">
       <c r="A39" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B39" s="3">
         <v>12</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D39" s="3"/>
       <c r="E39" s="4" t="s">
@@ -1589,13 +1590,13 @@
     </row>
     <row r="40" spans="1:8" ht="33">
       <c r="A40" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B40" s="3">
         <v>13</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D40" s="3"/>
       <c r="E40" s="4" t="s">
@@ -1607,13 +1608,13 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B41" s="3">
         <v>14</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D41" s="3"/>
       <c r="E41" s="4" t="s">
@@ -1625,13 +1626,13 @@
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B42" s="3">
         <v>1</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D42" s="3"/>
       <c r="E42" s="4" t="s">
@@ -1643,13 +1644,13 @@
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B43" s="3">
         <v>2</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D43" s="3"/>
       <c r="E43" s="4" t="s">
@@ -1661,13 +1662,13 @@
     </row>
     <row r="44" spans="1:8" ht="33">
       <c r="A44" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B44" s="3">
         <v>3</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D44" s="3"/>
       <c r="E44" s="4" t="s">
@@ -1679,13 +1680,13 @@
     </row>
     <row r="45" spans="1:8" ht="33">
       <c r="A45" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B45" s="3">
         <v>4</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D45" s="3"/>
       <c r="E45" s="4" t="s">
@@ -1697,17 +1698,17 @@
     </row>
     <row r="46" spans="1:8" ht="33">
       <c r="A46" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B46" s="3">
         <v>5</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D46" s="3"/>
       <c r="E46" s="4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -1715,13 +1716,13 @@
     </row>
     <row r="47" spans="1:8" ht="33">
       <c r="A47" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B47" s="3">
         <v>6</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="4" t="s">
@@ -1733,13 +1734,13 @@
     </row>
     <row r="48" spans="1:8" ht="33">
       <c r="A48" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" s="3">
         <v>1</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D48" s="3"/>
       <c r="E48" s="4" t="s">
@@ -1751,13 +1752,13 @@
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B49" s="3">
         <v>2</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="4" t="s">
@@ -1769,13 +1770,13 @@
     </row>
     <row r="50" spans="1:8" ht="33">
       <c r="A50" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B50" s="3">
         <v>3</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D50" s="3"/>
       <c r="E50" s="4" t="s">
@@ -1787,13 +1788,13 @@
     </row>
     <row r="51" spans="1:8" ht="33">
       <c r="A51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B51" s="3">
         <v>1</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="4" t="s">
@@ -1805,13 +1806,13 @@
     </row>
     <row r="52" spans="1:8" ht="33">
       <c r="A52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B52" s="3">
         <v>2</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="4" t="s">
@@ -1823,13 +1824,13 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B53" s="3">
         <v>3</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="4" t="s">
